--- a/labs/lab-07-custom-dashboard-skill/data/templates/Northstar_Dashboard_Starter.xlsx
+++ b/labs/lab-07-custom-dashboard-skill/data/templates/Northstar_Dashboard_Starter.xlsx
@@ -13,19 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter_Lists" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter_Lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Dashboard'!$A$1:$D$12</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -563,7 +556,181 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1333,7 +1500,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="3" t="n">
         <v>46278</v>
       </c>
@@ -1973,7 +2140,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="3" t="n">
         <v>46266</v>
       </c>
@@ -3261,7 +3428,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="3" t="n">
         <v>46242</v>
       </c>
@@ -4549,7 +4716,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="3" t="n">
         <v>46218</v>
       </c>
@@ -5189,7 +5356,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="3" t="n">
         <v>46286</v>
       </c>
@@ -6477,7 +6644,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="3" t="n">
         <v>46262</v>
       </c>
@@ -7092,7 +7259,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7298,7 +7464,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7480,7 +7645,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7535,7 +7699,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7579,12 +7742,10 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7595,7 +7756,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -7660,35 +7893,104 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>## OUTPUT AND REVIEW</t>
+          <t>## DASHBOARD LAYOUT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+          <t>Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+          <t>Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>## DASHBOARD STYLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>## OUTPUT AND REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
+    <row r="23">
+      <c r="A23" s="2">
         <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -7696,7 +7998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7864,7 +8166,6 @@
       <c r="D12" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
   <dataValidations count="4">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>'Filter_Lists'!$A$1:$A$6</formula1>
@@ -7881,179 +8182,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Woodlands Hub</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Leak Repair</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Aisha Tan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jurong Depot</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Valve Repair</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ben Lim</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tampines Centre</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pipe Replacement</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chloe Goh</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Paya Lebar Office</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pump Service</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Daniel Lee</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Changi Workshop</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Meter Service</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Elena Ong</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Farid Rahman</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Grace Ng</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Hari Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/labs/lab-07-custom-dashboard-skill/data/templates/Northstar_Dashboard_Starter.xlsx
+++ b/labs/lab-07-custom-dashboard-skill/data/templates/Northstar_Dashboard_Starter.xlsx
@@ -546,12 +546,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rejoin</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>This input is a deterministic checkpoint, not proof of your Copilot output.</t>
+          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-07-custom-dashboard-skill/data/templates/Northstar_Dashboard_Starter.xlsx
+++ b/labs/lab-07-custom-dashboard-skill/data/templates/Northstar_Dashboard_Starter.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
+          <t>Synthetic training data. Work on this file in your lab folder.</t>
         </is>
       </c>
     </row>
